--- a/referral_form_templates/036_marketing_web_developer_referral_form--referral_form_templates.xlsx
+++ b/referral_form_templates/036_marketing_web_developer_referral_form--referral_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>submission_date</t>
+          <t>submission_date_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Submission Date</t>
+          <t>Submission Date 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>submission_status</t>
+          <t>submission_status_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Submission Status</t>
+          <t>Submission Status 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>submission_comments</t>
+          <t>submission_comments_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Submission Comments</t>
+          <t>Submission Comments 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>project_url</t>
+          <t>project_url_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Project URL</t>
+          <t>Project Url 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>assigned_tool_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Assigned Tool 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>submission_status_2</t>
+          <t>submission_status_2_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Submission Status 2</t>
+          <t>Submission Status 2 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1194,7 +1194,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>submission_status_choices</t>
+          <t>submission_status_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>submission_status_choices</t>
+          <t>submission_status_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1262,7 +1262,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>submission_status_2_choices</t>
+          <t>submission_status_2_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,7 +1279,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>submission_status_2_choices</t>
+          <t>submission_status_2_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
